--- a/EL.xlsx
+++ b/EL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DCB7073-9104-494D-914E-9ADFFFC9BC8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35500E27-6495-4035-A011-933F2FE2FC3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="1" xr2:uid="{987A5598-021A-421D-8295-FCBBAB2A08B8}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{987A5598-021A-421D-8295-FCBBAB2A08B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
   <si>
     <t>Estee Lauder</t>
   </si>
@@ -176,21 +176,40 @@
   <si>
     <t>Mac, Niod, Origins, Smashbox, The Oridinary, Tom Ford, Too Faced</t>
   </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -247,19 +266,23 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -615,7 +638,7 @@
         <v>2</v>
       </c>
       <c r="K2" s="2">
-        <v>63.49</v>
+        <v>111.2</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -623,11 +646,11 @@
         <v>3</v>
       </c>
       <c r="K3" s="3">
-        <f>234.209951+125.542029</f>
-        <v>359.75198</v>
+        <f>247.219699+114.507344</f>
+        <v>361.72704299999998</v>
       </c>
-      <c r="L3" s="4" t="s">
-        <v>9</v>
+      <c r="L3" s="8" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -639,7 +662,7 @@
       </c>
       <c r="K4" s="3">
         <f>+K2*K3</f>
-        <v>22840.653210200002</v>
+        <v>40224.047181599999</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -647,10 +670,10 @@
         <v>5</v>
       </c>
       <c r="K5" s="3">
-        <v>2631</v>
+        <v>3082</v>
       </c>
-      <c r="L5" s="4" t="s">
-        <v>9</v>
+      <c r="L5" s="8" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -658,11 +681,11 @@
         <v>6</v>
       </c>
       <c r="K6" s="3">
-        <f>3+7298</f>
-        <v>7301</v>
+        <f>3+7319</f>
+        <v>7322</v>
       </c>
-      <c r="L6" s="4" t="s">
-        <v>9</v>
+      <c r="L6" s="8" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -671,7 +694,7 @@
       </c>
       <c r="K7" s="3">
         <f>+K4-K5+K6</f>
-        <v>27510.653210200002</v>
+        <v>44464.047181599999</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
@@ -747,6 +770,18 @@
       <c r="J2" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="K2" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -759,13 +794,17 @@
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+      <c r="H3" s="3">
+        <v>1921</v>
+      </c>
       <c r="I3" s="3">
         <v>1807</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
+      <c r="L3" s="3">
+        <v>2054</v>
+      </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
@@ -795,13 +834,17 @@
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="H4" s="3">
+        <v>1150</v>
+      </c>
       <c r="I4" s="3">
         <v>1035</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
+      <c r="L4" s="3">
+        <v>1164</v>
+      </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
@@ -831,13 +874,17 @@
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="H5" s="3">
+        <v>744</v>
+      </c>
       <c r="I5" s="3">
         <v>557</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
+      <c r="L5" s="3">
+        <v>812</v>
+      </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
@@ -867,13 +914,17 @@
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="H6" s="3">
+        <v>159</v>
+      </c>
       <c r="I6" s="3">
         <v>126</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
+      <c r="L6" s="3">
+        <v>168</v>
+      </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
@@ -903,13 +954,17 @@
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="H7" s="3">
+        <v>30</v>
+      </c>
       <c r="I7" s="3">
         <v>25</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
+      <c r="L7" s="3">
+        <v>31</v>
+      </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
@@ -939,13 +994,17 @@
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="H8" s="3">
+        <v>1209</v>
+      </c>
       <c r="I8" s="3">
         <v>1052</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
+      <c r="L8" s="3">
+        <v>1218</v>
+      </c>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -975,13 +1034,17 @@
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="H9" s="3">
+        <v>1085</v>
+      </c>
       <c r="I9" s="3">
         <v>1358</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
+      <c r="L9" s="3">
+        <v>1183</v>
+      </c>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
@@ -1011,13 +1074,19 @@
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="H10" s="3">
+        <f>888+822</f>
+        <v>1710</v>
+      </c>
       <c r="I10" s="3">
         <v>1140</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
+      <c r="L10" s="3">
+        <f>900+928</f>
+        <v>1828</v>
+      </c>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
@@ -1047,13 +1116,17 @@
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
+      <c r="H11" s="7">
+        <v>4004</v>
+      </c>
       <c r="I11" s="7">
         <v>3550</v>
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
+      <c r="L11" s="7">
+        <v>4229</v>
+      </c>
       <c r="M11" s="7"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
@@ -1083,13 +1156,17 @@
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="H12" s="3">
+        <v>957</v>
+      </c>
       <c r="I12" s="3">
         <v>889</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
+      <c r="L12" s="3">
+        <v>994</v>
+      </c>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
@@ -1134,18 +1211,24 @@
       </c>
       <c r="H13" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3047</v>
       </c>
       <c r="I13" s="3">
         <f>+I11-I12</f>
         <v>2661</v>
       </c>
       <c r="J13" s="3">
-        <f t="shared" ref="J13" si="1">+J11-J12</f>
+        <f t="shared" ref="J13:L13" si="1">+J11-J12</f>
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
+      <c r="K13" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="3">
+        <f t="shared" si="1"/>
+        <v>3235</v>
+      </c>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
@@ -1175,13 +1258,17 @@
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+      <c r="H14" s="3">
+        <v>2585</v>
+      </c>
       <c r="I14" s="3">
         <v>2258</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
+      <c r="L14" s="3">
+        <v>2627</v>
+      </c>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
@@ -1211,13 +1298,18 @@
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="H15" s="3">
+        <f>181+861</f>
+        <v>1042</v>
+      </c>
       <c r="I15" s="3">
         <v>97</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
+      <c r="L15" s="3">
+        <v>207</v>
+      </c>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
@@ -1241,7 +1333,7 @@
         <v>23</v>
       </c>
       <c r="C16" s="3">
-        <f t="shared" ref="C16:J16" si="2">+C13-SUM(C14:C15)</f>
+        <f t="shared" ref="C16:L16" si="2">+C13-SUM(C14:C15)</f>
         <v>0</v>
       </c>
       <c r="D16" s="3">
@@ -1262,7 +1354,7 @@
       </c>
       <c r="H16" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-580</v>
       </c>
       <c r="I16" s="3">
         <f t="shared" si="2"/>
@@ -1272,8 +1364,14 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
+      <c r="K16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="3">
+        <f t="shared" si="2"/>
+        <v>401</v>
+      </c>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
@@ -1303,13 +1401,17 @@
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
+      <c r="H17" s="3">
+        <v>90</v>
+      </c>
       <c r="I17" s="3">
         <v>87</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
+      <c r="L17" s="3">
+        <v>85</v>
+      </c>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
@@ -1339,13 +1441,17 @@
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
+      <c r="H18" s="3">
+        <v>23</v>
+      </c>
       <c r="I18" s="3">
         <v>27</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
+      <c r="L18" s="3">
+        <v>21</v>
+      </c>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
@@ -1375,13 +1481,17 @@
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
+      <c r="H19" s="3">
+        <v>3</v>
+      </c>
       <c r="I19" s="3">
         <v>5</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
+      <c r="L19" s="3">
+        <v>4</v>
+      </c>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
@@ -1426,18 +1536,24 @@
       </c>
       <c r="H20" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-650</v>
       </c>
       <c r="I20" s="3">
         <f>+I16-I17+I18-I19</f>
         <v>241</v>
       </c>
       <c r="J20" s="3">
-        <f t="shared" ref="J20" si="4">+J16-J17+J18-J19</f>
+        <f t="shared" ref="J20:L20" si="4">+J16-J17+J18-J19</f>
         <v>0</v>
       </c>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
+      <c r="K20" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <f t="shared" si="4"/>
+        <v>333</v>
+      </c>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
@@ -1467,13 +1583,17 @@
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
+      <c r="H21" s="3">
+        <v>-60</v>
+      </c>
       <c r="I21" s="3">
         <v>82</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
+      <c r="L21" s="3">
+        <v>171</v>
+      </c>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
@@ -1518,7 +1638,7 @@
       </c>
       <c r="H22" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-590</v>
       </c>
       <c r="I22" s="3">
         <f>+I20-I21</f>
@@ -1528,8 +1648,14 @@
         <f>+J20-J21</f>
         <v>0</v>
       </c>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
+      <c r="K22" s="3">
+        <f t="shared" ref="K22:L22" si="6">+K20-K21</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <f t="shared" si="6"/>
+        <v>162</v>
+      </c>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
@@ -1559,13 +1685,17 @@
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
+      <c r="H23" s="3">
+        <v>0</v>
+      </c>
       <c r="I23" s="3">
         <v>0</v>
       </c>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
+      <c r="L23" s="3">
+        <v>0</v>
+      </c>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -1589,39 +1719,45 @@
         <v>31</v>
       </c>
       <c r="C24" s="3">
-        <f t="shared" ref="C24:H24" si="6">+C22-C23</f>
+        <f t="shared" ref="C24:H24" si="7">+C22-C23</f>
         <v>0</v>
       </c>
       <c r="D24" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E24" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>330</v>
       </c>
       <c r="F24" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G24" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H24" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>-590</v>
       </c>
       <c r="I24" s="3">
         <f>+I22-I23</f>
         <v>159</v>
       </c>
       <c r="J24" s="3">
-        <f t="shared" ref="J24" si="7">+J22-J23</f>
+        <f t="shared" ref="J24:L24" si="8">+J22-J23</f>
         <v>0</v>
       </c>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
+      <c r="K24" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <f t="shared" si="8"/>
+        <v>162</v>
+      </c>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
@@ -1673,40 +1809,46 @@
       <c r="B26" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="3" t="e">
-        <f t="shared" ref="C26:H26" si="8">+C24/C27</f>
+      <c r="C26" s="9" t="e">
+        <f t="shared" ref="C26:L26" si="9">+C24/C27</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D26" s="3" t="e">
-        <f t="shared" si="8"/>
+      <c r="D26" s="9" t="e">
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E26" s="3">
-        <f t="shared" si="8"/>
+      <c r="E26" s="9">
+        <f t="shared" si="9"/>
         <v>0.91896407685881365</v>
       </c>
-      <c r="F26" s="3" t="e">
-        <f t="shared" si="8"/>
+      <c r="F26" s="9" t="e">
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G26" s="3" t="e">
-        <f t="shared" si="8"/>
+      <c r="G26" s="9" t="e">
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H26" s="3" t="e">
-        <f t="shared" si="8"/>
+      <c r="H26" s="9">
+        <f t="shared" si="9"/>
+        <v>-1.6388888888888888</v>
+      </c>
+      <c r="I26" s="9">
+        <f t="shared" si="9"/>
+        <v>0.44129891756869272</v>
+      </c>
+      <c r="J26" s="9" t="e">
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I26" s="3">
-        <f>+I24/I27</f>
-        <v>0.44129891756869272</v>
-      </c>
-      <c r="J26" s="3" t="e">
-        <f t="shared" ref="J26" si="9">+J24/J27</f>
+      <c r="K26" s="9" t="e">
+        <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
+      <c r="L26" s="9">
+        <f t="shared" ref="J26:L26" si="10">+L24/L27</f>
+        <v>0.44739022369511183</v>
+      </c>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
@@ -1736,13 +1878,17 @@
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
+      <c r="H27" s="3">
+        <v>360</v>
+      </c>
       <c r="I27" s="3">
         <v>360.3</v>
       </c>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
+      <c r="L27" s="3">
+        <v>362.1</v>
+      </c>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>

--- a/EL.xlsx
+++ b/EL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35500E27-6495-4035-A011-933F2FE2FC3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E46267-F09B-424F-8ED5-586D2440CAEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{987A5598-021A-421D-8295-FCBBAB2A08B8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
   <si>
     <t>Estee Lauder</t>
   </si>
@@ -188,6 +188,18 @@
   <si>
     <t>Q426</t>
   </si>
+  <si>
+    <t>Revenue Growth</t>
+  </si>
+  <si>
+    <t>Gross Margin</t>
+  </si>
+  <si>
+    <t>Operating Margin</t>
+  </si>
+  <si>
+    <t>Tax Rate</t>
+  </si>
 </sst>
 </file>
 
@@ -195,15 +207,21 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -246,6 +264,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -264,29 +289,34 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -793,7 +823,9 @@
         <v>2060</v>
       </c>
       <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+      <c r="G3" s="3">
+        <v>1529</v>
+      </c>
       <c r="H3" s="3">
         <v>1921</v>
       </c>
@@ -801,7 +833,9 @@
         <v>1807</v>
       </c>
       <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
+      <c r="K3" s="3">
+        <v>1575</v>
+      </c>
       <c r="L3" s="3">
         <v>2054</v>
       </c>
@@ -833,7 +867,9 @@
         <v>1136</v>
       </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="G4" s="3">
+        <v>1038</v>
+      </c>
       <c r="H4" s="3">
         <v>1150</v>
       </c>
@@ -841,7 +877,9 @@
         <v>1035</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+      <c r="K4" s="3">
+        <v>1030</v>
+      </c>
       <c r="L4" s="3">
         <v>1164</v>
       </c>
@@ -873,7 +911,9 @@
         <v>575</v>
       </c>
       <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="G5" s="3">
+        <v>630</v>
+      </c>
       <c r="H5" s="3">
         <v>744</v>
       </c>
@@ -881,7 +921,9 @@
         <v>557</v>
       </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
+      <c r="K5" s="3">
+        <v>721</v>
+      </c>
       <c r="L5" s="3">
         <v>812</v>
       </c>
@@ -913,7 +955,9 @@
         <v>143</v>
       </c>
       <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="G6" s="3">
+        <v>139</v>
+      </c>
       <c r="H6" s="3">
         <v>159</v>
       </c>
@@ -921,7 +965,9 @@
         <v>126</v>
       </c>
       <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
+      <c r="K6" s="3">
+        <v>129</v>
+      </c>
       <c r="L6" s="3">
         <v>168</v>
       </c>
@@ -953,7 +999,9 @@
         <v>26</v>
       </c>
       <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="G7" s="3">
+        <v>25</v>
+      </c>
       <c r="H7" s="3">
         <v>30</v>
       </c>
@@ -961,7 +1009,9 @@
         <v>25</v>
       </c>
       <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
+      <c r="K7" s="3">
+        <v>5</v>
+      </c>
       <c r="L7" s="3">
         <v>31</v>
       </c>
@@ -993,7 +1043,9 @@
         <v>1117</v>
       </c>
       <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
+      <c r="G8" s="3">
+        <v>1197</v>
+      </c>
       <c r="H8" s="3">
         <v>1209</v>
       </c>
@@ -1001,7 +1053,9 @@
         <v>1052</v>
       </c>
       <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="K8" s="3">
+        <v>1174</v>
+      </c>
       <c r="L8" s="3">
         <v>1218</v>
       </c>
@@ -1033,7 +1087,9 @@
         <v>1647</v>
       </c>
       <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+      <c r="G9" s="3">
+        <v>868</v>
+      </c>
       <c r="H9" s="3">
         <v>1085</v>
       </c>
@@ -1041,7 +1097,9 @@
         <v>1358</v>
       </c>
       <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="K9" s="3">
+        <v>901</v>
+      </c>
       <c r="L9" s="3">
         <v>1183</v>
       </c>
@@ -1073,7 +1131,10 @@
         <v>1176</v>
       </c>
       <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="G10" s="3">
+        <f>806+490</f>
+        <v>1296</v>
+      </c>
       <c r="H10" s="3">
         <f>888+822</f>
         <v>1710</v>
@@ -1082,7 +1143,10 @@
         <v>1140</v>
       </c>
       <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="K10" s="3">
+        <f>873+532</f>
+        <v>1405</v>
+      </c>
       <c r="L10" s="3">
         <f>900+928</f>
         <v>1828</v>
@@ -1115,7 +1179,9 @@
         <v>3940</v>
       </c>
       <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
+      <c r="G11" s="7">
+        <v>3361</v>
+      </c>
       <c r="H11" s="7">
         <v>4004</v>
       </c>
@@ -1123,7 +1189,9 @@
         <v>3550</v>
       </c>
       <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
+      <c r="K11" s="7">
+        <v>3481</v>
+      </c>
       <c r="L11" s="7">
         <v>4229</v>
       </c>
@@ -1155,7 +1223,9 @@
         <v>1107</v>
       </c>
       <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
+      <c r="G12" s="3">
+        <v>928</v>
+      </c>
       <c r="H12" s="3">
         <v>957</v>
       </c>
@@ -1163,7 +1233,9 @@
         <v>889</v>
       </c>
       <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+      <c r="K12" s="3">
+        <v>927</v>
+      </c>
       <c r="L12" s="3">
         <v>994</v>
       </c>
@@ -1207,7 +1279,7 @@
       </c>
       <c r="G13" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2433</v>
       </c>
       <c r="H13" s="3">
         <f t="shared" si="0"/>
@@ -1223,7 +1295,7 @@
       </c>
       <c r="K13" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2554</v>
       </c>
       <c r="L13" s="3">
         <f t="shared" si="1"/>
@@ -1257,7 +1329,9 @@
         <v>2284</v>
       </c>
       <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
+      <c r="G14" s="3">
+        <v>2298</v>
+      </c>
       <c r="H14" s="3">
         <v>2585</v>
       </c>
@@ -1265,7 +1339,9 @@
         <v>2258</v>
       </c>
       <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
+      <c r="K14" s="3">
+        <v>2296</v>
+      </c>
       <c r="L14" s="3">
         <v>2627</v>
       </c>
@@ -1297,7 +1373,10 @@
         <v>18</v>
       </c>
       <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+      <c r="G15" s="3">
+        <f>97+159</f>
+        <v>256</v>
+      </c>
       <c r="H15" s="3">
         <f>181+861</f>
         <v>1042</v>
@@ -1306,7 +1385,9 @@
         <v>97</v>
       </c>
       <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
+      <c r="K15" s="3">
+        <v>89</v>
+      </c>
       <c r="L15" s="3">
         <v>207</v>
       </c>
@@ -1350,7 +1431,7 @@
       </c>
       <c r="G16" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-121</v>
       </c>
       <c r="H16" s="3">
         <f t="shared" si="2"/>
@@ -1366,7 +1447,7 @@
       </c>
       <c r="K16" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="L16" s="3">
         <f t="shared" si="2"/>
@@ -1400,7 +1481,9 @@
         <v>94</v>
       </c>
       <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
+      <c r="G17" s="3">
+        <v>92</v>
+      </c>
       <c r="H17" s="3">
         <v>90</v>
       </c>
@@ -1408,7 +1491,9 @@
         <v>87</v>
       </c>
       <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
+      <c r="K17" s="3">
+        <v>86</v>
+      </c>
       <c r="L17" s="3">
         <v>85</v>
       </c>
@@ -1440,7 +1525,9 @@
         <v>45</v>
       </c>
       <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
+      <c r="G18" s="3">
+        <v>35</v>
+      </c>
       <c r="H18" s="3">
         <v>23</v>
       </c>
@@ -1448,7 +1535,9 @@
         <v>27</v>
       </c>
       <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
+      <c r="K18" s="3">
+        <v>30</v>
+      </c>
       <c r="L18" s="3">
         <v>21</v>
       </c>
@@ -1480,7 +1569,9 @@
         <v>-4</v>
       </c>
       <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
+      <c r="G19" s="3">
+        <v>2</v>
+      </c>
       <c r="H19" s="3">
         <v>3</v>
       </c>
@@ -1488,7 +1579,9 @@
         <v>5</v>
       </c>
       <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
+      <c r="K19" s="3">
+        <v>4</v>
+      </c>
       <c r="L19" s="3">
         <v>4</v>
       </c>
@@ -1532,7 +1625,7 @@
       </c>
       <c r="G20" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-180</v>
       </c>
       <c r="H20" s="3">
         <f t="shared" si="3"/>
@@ -1548,7 +1641,7 @@
       </c>
       <c r="K20" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="L20" s="3">
         <f t="shared" si="4"/>
@@ -1582,7 +1675,9 @@
         <v>151</v>
       </c>
       <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
+      <c r="G21" s="3">
+        <v>-24</v>
+      </c>
       <c r="H21" s="3">
         <v>-60</v>
       </c>
@@ -1590,7 +1685,9 @@
         <v>82</v>
       </c>
       <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
+      <c r="K21" s="3">
+        <v>62</v>
+      </c>
       <c r="L21" s="3">
         <v>171</v>
       </c>
@@ -1634,7 +1731,7 @@
       </c>
       <c r="G22" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-156</v>
       </c>
       <c r="H22" s="3">
         <f t="shared" si="5"/>
@@ -1650,7 +1747,7 @@
       </c>
       <c r="K22" s="3">
         <f t="shared" ref="K22:L22" si="6">+K20-K21</f>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="L22" s="3">
         <f t="shared" si="6"/>
@@ -1684,7 +1781,9 @@
         <v>5</v>
       </c>
       <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
       <c r="H23" s="3">
         <v>0</v>
       </c>
@@ -1692,7 +1791,9 @@
         <v>0</v>
       </c>
       <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
+      <c r="K23" s="3">
+        <v>0</v>
+      </c>
       <c r="L23" s="3">
         <v>0</v>
       </c>
@@ -1736,7 +1837,7 @@
       </c>
       <c r="G24" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-156</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" si="7"/>
@@ -1752,7 +1853,7 @@
       </c>
       <c r="K24" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="L24" s="3">
         <f t="shared" si="8"/>
@@ -1810,7 +1911,7 @@
         <v>32</v>
       </c>
       <c r="C26" s="9" t="e">
-        <f t="shared" ref="C26:L26" si="9">+C24/C27</f>
+        <f t="shared" ref="C26:K26" si="9">+C24/C27</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D26" s="9" t="e">
@@ -1825,9 +1926,9 @@
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G26" s="9" t="e">
+      <c r="G26" s="9">
         <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
+        <v>-0.43381535038932145</v>
       </c>
       <c r="H26" s="9">
         <f t="shared" si="9"/>
@@ -1841,12 +1942,12 @@
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K26" s="9" t="e">
+      <c r="K26" s="9">
         <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
+        <v>0.1301218161683278</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" ref="J26:L26" si="10">+L24/L27</f>
+        <f t="shared" ref="L26" si="10">+L24/L27</f>
         <v>0.44739022369511183</v>
       </c>
       <c r="M26" s="3"/>
@@ -1877,7 +1978,9 @@
         <v>359.1</v>
       </c>
       <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
+      <c r="G27" s="3">
+        <v>359.6</v>
+      </c>
       <c r="H27" s="3">
         <v>360</v>
       </c>
@@ -1885,7 +1988,9 @@
         <v>360.3</v>
       </c>
       <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
+      <c r="K27" s="3">
+        <v>361.2</v>
+      </c>
       <c r="L27" s="3">
         <v>362.1</v>
       </c>
@@ -1937,16 +2042,37 @@
       <c r="AC28" s="3"/>
     </row>
     <row r="29" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="B29" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
+      <c r="G29" s="11" t="e">
+        <f>+G11/C11-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H29" s="11" t="e">
+        <f>+H11/D11-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I29" s="11">
+        <f>+I11/E11-1</f>
+        <v>-9.898477157360408E-2</v>
+      </c>
+      <c r="J29" s="11" t="e">
+        <f>+J11/F11-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K29" s="11">
+        <f>+K11/G11-1</f>
+        <v>3.5703659625111683E-2</v>
+      </c>
+      <c r="L29" s="11">
+        <f>+L11/H11-1</f>
+        <v>5.6193806193806095E-2</v>
+      </c>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
@@ -1966,16 +2092,49 @@
       <c r="AC29" s="3"/>
     </row>
     <row r="30" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
+      <c r="B30" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" s="12" t="e">
+        <f t="shared" ref="C30:L30" si="11">+C13/C11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D30" s="12" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E30" s="12">
+        <f t="shared" si="11"/>
+        <v>0.71903553299492384</v>
+      </c>
+      <c r="F30" s="12" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G30" s="12">
+        <f t="shared" si="11"/>
+        <v>0.72389169889913718</v>
+      </c>
+      <c r="H30" s="12">
+        <f t="shared" si="11"/>
+        <v>0.76098901098901095</v>
+      </c>
+      <c r="I30" s="12">
+        <f t="shared" si="11"/>
+        <v>0.74957746478873244</v>
+      </c>
+      <c r="J30" s="12" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K30" s="12">
+        <f t="shared" si="11"/>
+        <v>0.73369721344441252</v>
+      </c>
+      <c r="L30" s="12">
+        <f>+L13/L11</f>
+        <v>0.76495625443367221</v>
+      </c>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
@@ -1995,16 +2154,49 @@
       <c r="AC30" s="3"/>
     </row>
     <row r="31" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
+      <c r="B31" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="12" t="e">
+        <f t="shared" ref="C31:L31" si="12">+C16/C11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D31" s="12" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E31" s="12">
+        <f t="shared" si="12"/>
+        <v>0.13477157360406092</v>
+      </c>
+      <c r="F31" s="12" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G31" s="12">
+        <f t="shared" si="12"/>
+        <v>-3.6001190121987506E-2</v>
+      </c>
+      <c r="H31" s="12">
+        <f t="shared" si="12"/>
+        <v>-0.14485514485514486</v>
+      </c>
+      <c r="I31" s="12">
+        <f t="shared" si="12"/>
+        <v>8.6197183098591548E-2</v>
+      </c>
+      <c r="J31" s="12" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K31" s="12">
+        <f t="shared" si="12"/>
+        <v>4.8549267451881643E-2</v>
+      </c>
+      <c r="L31" s="12">
+        <f>+L16/L11</f>
+        <v>9.4821470796878693E-2</v>
+      </c>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
@@ -2024,16 +2216,49 @@
       <c r="AC31" s="3"/>
     </row>
     <row r="32" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
+      <c r="B32" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="12" t="e">
+        <f t="shared" ref="C32:L32" si="13">+C21/C20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D32" s="12" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E32" s="12">
+        <f t="shared" si="13"/>
+        <v>0.31069958847736623</v>
+      </c>
+      <c r="F32" s="12" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G32" s="12">
+        <f t="shared" si="13"/>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="H32" s="12">
+        <f t="shared" si="13"/>
+        <v>9.2307692307692313E-2</v>
+      </c>
+      <c r="I32" s="12">
+        <f t="shared" si="13"/>
+        <v>0.34024896265560167</v>
+      </c>
+      <c r="J32" s="12" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K32" s="12">
+        <f t="shared" si="13"/>
+        <v>0.56880733944954132</v>
+      </c>
+      <c r="L32" s="12">
+        <f>+L21/L20</f>
+        <v>0.51351351351351349</v>
+      </c>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>

--- a/EL.xlsx
+++ b/EL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E46267-F09B-424F-8ED5-586D2440CAEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{626A726A-003E-476D-9665-1C1AA0E72F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{987A5598-021A-421D-8295-FCBBAB2A08B8}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{987A5598-021A-421D-8295-FCBBAB2A08B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -209,13 +209,19 @@
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -291,27 +297,30 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -668,7 +677,7 @@
         <v>2</v>
       </c>
       <c r="K2" s="2">
-        <v>111.2</v>
+        <v>80.58</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -676,11 +685,11 @@
         <v>3</v>
       </c>
       <c r="K3" s="3">
-        <f>247.219699+114.507344</f>
-        <v>361.72704299999998</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>47</v>
+        <f>247.287571+114.507344</f>
+        <v>361.794915</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -692,7 +701,7 @@
       </c>
       <c r="K4" s="3">
         <f>+K2*K3</f>
-        <v>40224.047181599999</v>
+        <v>29153.4342507</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -700,10 +709,10 @@
         <v>5</v>
       </c>
       <c r="K5" s="3">
-        <v>3082</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>47</v>
+        <v>3126</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -711,11 +720,11 @@
         <v>6</v>
       </c>
       <c r="K6" s="3">
-        <f>3+7319</f>
-        <v>7322</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>47</v>
+        <f>502+6810</f>
+        <v>7312</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -724,7 +733,7 @@
       </c>
       <c r="K7" s="3">
         <f>+K4-K5+K6</f>
-        <v>44464.047181599999</v>
+        <v>33339.434250699996</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
@@ -839,7 +848,9 @@
       <c r="L3" s="3">
         <v>2054</v>
       </c>
-      <c r="M3" s="3"/>
+      <c r="M3" s="3">
+        <v>1856</v>
+      </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
@@ -883,7 +894,9 @@
       <c r="L4" s="3">
         <v>1164</v>
       </c>
-      <c r="M4" s="3"/>
+      <c r="M4" s="3">
+        <v>1072</v>
+      </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
@@ -927,7 +940,9 @@
       <c r="L5" s="3">
         <v>812</v>
       </c>
-      <c r="M5" s="3"/>
+      <c r="M5" s="3">
+        <v>628</v>
+      </c>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
@@ -971,7 +986,9 @@
       <c r="L6" s="3">
         <v>168</v>
       </c>
-      <c r="M6" s="3"/>
+      <c r="M6" s="3">
+        <v>128</v>
+      </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
@@ -1015,7 +1032,9 @@
       <c r="L7" s="3">
         <v>31</v>
       </c>
-      <c r="M7" s="3"/>
+      <c r="M7" s="3">
+        <v>28</v>
+      </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
@@ -1059,7 +1078,9 @@
       <c r="L8" s="3">
         <v>1218</v>
       </c>
-      <c r="M8" s="3"/>
+      <c r="M8" s="3">
+        <v>1076</v>
+      </c>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
@@ -1103,7 +1124,9 @@
       <c r="L9" s="3">
         <v>1183</v>
       </c>
-      <c r="M9" s="3"/>
+      <c r="M9" s="3">
+        <v>859</v>
+      </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
@@ -1151,7 +1174,10 @@
         <f>900+928</f>
         <v>1828</v>
       </c>
-      <c r="M10" s="3"/>
+      <c r="M10" s="3">
+        <f>1003+774</f>
+        <v>1777</v>
+      </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -1195,7 +1221,9 @@
       <c r="L11" s="7">
         <v>4229</v>
       </c>
-      <c r="M11" s="7"/>
+      <c r="M11" s="7">
+        <v>3712</v>
+      </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
@@ -1239,7 +1267,9 @@
       <c r="L12" s="3">
         <v>994</v>
       </c>
-      <c r="M12" s="3"/>
+      <c r="M12" s="3">
+        <v>876</v>
+      </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -1290,7 +1320,7 @@
         <v>2661</v>
       </c>
       <c r="J13" s="3">
-        <f t="shared" ref="J13:L13" si="1">+J11-J12</f>
+        <f t="shared" ref="J13:M13" si="1">+J11-J12</f>
         <v>0</v>
       </c>
       <c r="K13" s="3">
@@ -1301,7 +1331,10 @@
         <f t="shared" si="1"/>
         <v>3235</v>
       </c>
-      <c r="M13" s="3"/>
+      <c r="M13" s="3">
+        <f t="shared" si="1"/>
+        <v>2836</v>
+      </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -1345,7 +1378,9 @@
       <c r="L14" s="3">
         <v>2627</v>
       </c>
-      <c r="M14" s="3"/>
+      <c r="M14" s="3">
+        <v>2279</v>
+      </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -1391,7 +1426,10 @@
       <c r="L15" s="3">
         <v>207</v>
       </c>
-      <c r="M15" s="3"/>
+      <c r="M15" s="3">
+        <f>224+84</f>
+        <v>308</v>
+      </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -1414,7 +1452,7 @@
         <v>23</v>
       </c>
       <c r="C16" s="3">
-        <f t="shared" ref="C16:L16" si="2">+C13-SUM(C14:C15)</f>
+        <f t="shared" ref="C16:M16" si="2">+C13-SUM(C14:C15)</f>
         <v>0</v>
       </c>
       <c r="D16" s="3">
@@ -1453,7 +1491,10 @@
         <f t="shared" si="2"/>
         <v>401</v>
       </c>
-      <c r="M16" s="3"/>
+      <c r="M16" s="3">
+        <f t="shared" si="2"/>
+        <v>249</v>
+      </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -1497,7 +1538,9 @@
       <c r="L17" s="3">
         <v>85</v>
       </c>
-      <c r="M17" s="3"/>
+      <c r="M17" s="3">
+        <v>82</v>
+      </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -1541,7 +1584,9 @@
       <c r="L18" s="3">
         <v>21</v>
       </c>
-      <c r="M18" s="3"/>
+      <c r="M18" s="3">
+        <v>15</v>
+      </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -1585,7 +1630,9 @@
       <c r="L19" s="3">
         <v>4</v>
       </c>
-      <c r="M19" s="3"/>
+      <c r="M19" s="3">
+        <v>3</v>
+      </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -1636,7 +1683,7 @@
         <v>241</v>
       </c>
       <c r="J20" s="3">
-        <f t="shared" ref="J20:L20" si="4">+J16-J17+J18-J19</f>
+        <f t="shared" ref="J20:M20" si="4">+J16-J17+J18-J19</f>
         <v>0</v>
       </c>
       <c r="K20" s="3">
@@ -1647,7 +1694,10 @@
         <f t="shared" si="4"/>
         <v>333</v>
       </c>
-      <c r="M20" s="3"/>
+      <c r="M20" s="3">
+        <f t="shared" si="4"/>
+        <v>179</v>
+      </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
@@ -1691,7 +1741,9 @@
       <c r="L21" s="3">
         <v>171</v>
       </c>
-      <c r="M21" s="3"/>
+      <c r="M21" s="3">
+        <v>90</v>
+      </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -1746,14 +1798,17 @@
         <v>0</v>
       </c>
       <c r="K22" s="3">
-        <f t="shared" ref="K22:L22" si="6">+K20-K21</f>
+        <f t="shared" ref="K22:M22" si="6">+K20-K21</f>
         <v>47</v>
       </c>
       <c r="L22" s="3">
         <f t="shared" si="6"/>
         <v>162</v>
       </c>
-      <c r="M22" s="3"/>
+      <c r="M22" s="3">
+        <f t="shared" si="6"/>
+        <v>89</v>
+      </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
@@ -1797,7 +1852,9 @@
       <c r="L23" s="3">
         <v>0</v>
       </c>
-      <c r="M23" s="3"/>
+      <c r="M23" s="3">
+        <v>0</v>
+      </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -1848,7 +1905,7 @@
         <v>159</v>
       </c>
       <c r="J24" s="3">
-        <f t="shared" ref="J24:L24" si="8">+J22-J23</f>
+        <f t="shared" ref="J24:M24" si="8">+J22-J23</f>
         <v>0</v>
       </c>
       <c r="K24" s="3">
@@ -1859,7 +1916,10 @@
         <f t="shared" si="8"/>
         <v>162</v>
       </c>
-      <c r="M24" s="3"/>
+      <c r="M24" s="3">
+        <f t="shared" si="8"/>
+        <v>89</v>
+      </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
@@ -1947,10 +2007,13 @@
         <v>0.1301218161683278</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" ref="L26" si="10">+L24/L27</f>
+        <f t="shared" ref="L26:M26" si="10">+L24/L27</f>
         <v>0.44739022369511183</v>
       </c>
-      <c r="M26" s="3"/>
+      <c r="M26" s="9">
+        <f t="shared" si="10"/>
+        <v>0.2453818582850841</v>
+      </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
@@ -1994,7 +2057,9 @@
       <c r="L27" s="3">
         <v>362.1</v>
       </c>
-      <c r="M27" s="3"/>
+      <c r="M27" s="3">
+        <v>362.7</v>
+      </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
@@ -2042,38 +2107,41 @@
       <c r="AC28" s="3"/>
     </row>
     <row r="29" spans="2:29" x14ac:dyDescent="0.2">
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="11" t="e">
-        <f>+G11/C11-1</f>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="13" t="e">
+        <f t="shared" ref="G29:M29" si="11">+G11/C11-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H29" s="11" t="e">
-        <f>+H11/D11-1</f>
+      <c r="H29" s="13" t="e">
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I29" s="11">
-        <f>+I11/E11-1</f>
+      <c r="I29" s="13">
+        <f t="shared" si="11"/>
         <v>-9.898477157360408E-2</v>
       </c>
-      <c r="J29" s="11" t="e">
-        <f>+J11/F11-1</f>
+      <c r="J29" s="13" t="e">
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K29" s="11">
-        <f>+K11/G11-1</f>
+      <c r="K29" s="13">
+        <f t="shared" si="11"/>
         <v>3.5703659625111683E-2</v>
       </c>
-      <c r="L29" s="11">
-        <f>+L11/H11-1</f>
+      <c r="L29" s="13">
+        <f t="shared" si="11"/>
         <v>5.6193806193806095E-2</v>
       </c>
-      <c r="M29" s="3"/>
+      <c r="M29" s="13">
+        <f t="shared" si="11"/>
+        <v>4.5633802816901436E-2</v>
+      </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
@@ -2095,47 +2163,50 @@
       <c r="B30" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C30" s="12" t="e">
-        <f t="shared" ref="C30:L30" si="11">+C13/C11</f>
+      <c r="C30" s="11" t="e">
+        <f t="shared" ref="C30:K30" si="12">+C13/C11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D30" s="12" t="e">
-        <f t="shared" si="11"/>
+      <c r="D30" s="11" t="e">
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E30" s="12">
-        <f t="shared" si="11"/>
+      <c r="E30" s="11">
+        <f t="shared" si="12"/>
         <v>0.71903553299492384</v>
       </c>
-      <c r="F30" s="12" t="e">
-        <f t="shared" si="11"/>
+      <c r="F30" s="11" t="e">
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G30" s="12">
-        <f t="shared" si="11"/>
+      <c r="G30" s="11">
+        <f t="shared" si="12"/>
         <v>0.72389169889913718</v>
       </c>
-      <c r="H30" s="12">
-        <f t="shared" si="11"/>
+      <c r="H30" s="11">
+        <f t="shared" si="12"/>
         <v>0.76098901098901095</v>
       </c>
-      <c r="I30" s="12">
-        <f t="shared" si="11"/>
+      <c r="I30" s="11">
+        <f t="shared" si="12"/>
         <v>0.74957746478873244</v>
       </c>
-      <c r="J30" s="12" t="e">
-        <f t="shared" si="11"/>
+      <c r="J30" s="11" t="e">
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K30" s="12">
-        <f t="shared" si="11"/>
+      <c r="K30" s="11">
+        <f t="shared" si="12"/>
         <v>0.73369721344441252</v>
       </c>
-      <c r="L30" s="12">
+      <c r="L30" s="11">
         <f>+L13/L11</f>
         <v>0.76495625443367221</v>
       </c>
-      <c r="M30" s="3"/>
+      <c r="M30" s="11">
+        <f>+M13/M11</f>
+        <v>0.76400862068965514</v>
+      </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
@@ -2157,47 +2228,50 @@
       <c r="B31" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="12" t="e">
-        <f t="shared" ref="C31:L31" si="12">+C16/C11</f>
+      <c r="C31" s="11" t="e">
+        <f t="shared" ref="C31:K31" si="13">+C16/C11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D31" s="12" t="e">
-        <f t="shared" si="12"/>
+      <c r="D31" s="11" t="e">
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E31" s="12">
-        <f t="shared" si="12"/>
+      <c r="E31" s="11">
+        <f t="shared" si="13"/>
         <v>0.13477157360406092</v>
       </c>
-      <c r="F31" s="12" t="e">
-        <f t="shared" si="12"/>
+      <c r="F31" s="11" t="e">
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G31" s="12">
-        <f t="shared" si="12"/>
+      <c r="G31" s="11">
+        <f t="shared" si="13"/>
         <v>-3.6001190121987506E-2</v>
       </c>
-      <c r="H31" s="12">
-        <f t="shared" si="12"/>
+      <c r="H31" s="11">
+        <f t="shared" si="13"/>
         <v>-0.14485514485514486</v>
       </c>
-      <c r="I31" s="12">
-        <f t="shared" si="12"/>
+      <c r="I31" s="11">
+        <f t="shared" si="13"/>
         <v>8.6197183098591548E-2</v>
       </c>
-      <c r="J31" s="12" t="e">
-        <f t="shared" si="12"/>
+      <c r="J31" s="11" t="e">
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K31" s="12">
-        <f t="shared" si="12"/>
+      <c r="K31" s="11">
+        <f t="shared" si="13"/>
         <v>4.8549267451881643E-2</v>
       </c>
-      <c r="L31" s="12">
+      <c r="L31" s="11">
         <f>+L16/L11</f>
         <v>9.4821470796878693E-2</v>
       </c>
-      <c r="M31" s="3"/>
+      <c r="M31" s="11">
+        <f>+M16/M11</f>
+        <v>6.7079741379310345E-2</v>
+      </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
@@ -2219,47 +2293,50 @@
       <c r="B32" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="12" t="e">
-        <f t="shared" ref="C32:L32" si="13">+C21/C20</f>
+      <c r="C32" s="11" t="e">
+        <f t="shared" ref="C32:K32" si="14">+C21/C20</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D32" s="12" t="e">
-        <f t="shared" si="13"/>
+      <c r="D32" s="11" t="e">
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E32" s="12">
-        <f t="shared" si="13"/>
+      <c r="E32" s="11">
+        <f t="shared" si="14"/>
         <v>0.31069958847736623</v>
       </c>
-      <c r="F32" s="12" t="e">
-        <f t="shared" si="13"/>
+      <c r="F32" s="11" t="e">
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G32" s="12">
-        <f t="shared" si="13"/>
+      <c r="G32" s="11">
+        <f t="shared" si="14"/>
         <v>0.13333333333333333</v>
       </c>
-      <c r="H32" s="12">
-        <f t="shared" si="13"/>
+      <c r="H32" s="11">
+        <f t="shared" si="14"/>
         <v>9.2307692307692313E-2</v>
       </c>
-      <c r="I32" s="12">
-        <f t="shared" si="13"/>
+      <c r="I32" s="11">
+        <f t="shared" si="14"/>
         <v>0.34024896265560167</v>
       </c>
-      <c r="J32" s="12" t="e">
-        <f t="shared" si="13"/>
+      <c r="J32" s="11" t="e">
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K32" s="12">
-        <f t="shared" si="13"/>
+      <c r="K32" s="11">
+        <f t="shared" si="14"/>
         <v>0.56880733944954132</v>
       </c>
-      <c r="L32" s="12">
+      <c r="L32" s="11">
         <f>+L21/L20</f>
         <v>0.51351351351351349</v>
       </c>
-      <c r="M32" s="3"/>
+      <c r="M32" s="11">
+        <f>+M21/M20</f>
+        <v>0.5027932960893855</v>
+      </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
